--- a/data/trending_integrated_20261019_15.xlsx
+++ b/data/trending_integrated_20261019_15.xlsx
@@ -578,13 +578,13 @@
         <v>0.42</v>
       </c>
       <c r="E2" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G2" t="n">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>20670713280</v>
+        <v>20708828420</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9760</v>
+        <v>9700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.50%</t>
+          <t>'+14.79%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F3" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G3" t="n">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>38939153820</v>
+        <v>40027803035</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>명신산업, 테슬라 납품 비중 높은 가운데 저평가 매력 부각. 자사주 매입 발표로 추가 상승 기대감 형성.</t>
+          <t>명신산업, 테슬라 로드스터 수혜 및 매출 비중 언급. 저평가 및 수급 기대감 속에 급등했으나, 공매도 및 하락 경계 신호도 존재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['테슬라 납품', '저평가', '자사주 매입']</t>
+          <t>['테슬라', '저평가', '수급']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>169600</v>
+        <v>170700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.44%</t>
+          <t>'+2.09%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F4" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G4" t="n">
         <v>297</v>
@@ -794,7 +794,7 @@
         <v>75</v>
       </c>
       <c r="O4" t="n">
-        <v>602798384150</v>
+        <v>620476098400</v>
       </c>
       <c r="P4" t="n">
         <v>243500</v>
@@ -839,83 +839,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9060</v>
+        <v>218000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.55%</t>
+          <t>'+1.16%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.02</v>
+        <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>125</v>
+        <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>67</v>
+        <v>506</v>
       </c>
       <c r="G5" t="n">
-        <v>262</v>
+        <v>1811</v>
       </c>
       <c r="H5" t="n">
-        <v>1.74</v>
+        <v>45.99</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9010</v>
+        <v>215500</v>
       </c>
       <c r="K5" t="n">
-        <v>8810</v>
+        <v>207000</v>
       </c>
       <c r="L5" t="n">
-        <v>9500</v>
+        <v>219500</v>
       </c>
       <c r="M5" t="n">
-        <v>8510</v>
+        <v>206500</v>
       </c>
       <c r="N5" t="n">
-        <v>0.72</v>
+        <v>45.98</v>
       </c>
       <c r="O5" t="n">
-        <v>149843100170</v>
+        <v>2986042845750</v>
       </c>
       <c r="P5" t="n">
-        <v>9500</v>
+        <v>374500</v>
       </c>
       <c r="Q5" t="n">
-        <v>2270</v>
+        <v>94500</v>
       </c>
       <c r="R5" t="n">
-        <v>-235000</v>
+        <v>1564000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>718000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>HT로보틱스, 시장 전반의 하락세 속에서 특별한 근거 없이 개인 투자자들의 혼란과 손실 경험이 주로 언급됨.</t>
+          <t>삼성전자, 주주환원 요구와 함께 바닥 다지기 후 상승 기대감 표출. 외인 순매수 기록했으나 종가 하락 및 연기금 이탈 조짐.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['로봇주', '개인 투자', '시장']</t>
+          <t>['주주환원', '외인순매수', '바닥다지기']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14810</v>
+        <v>14860</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.54%</t>
+          <t>'+0.88%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G6" t="n">
-        <v>341</v>
+        <v>366</v>
       </c>
       <c r="H6" t="n">
         <v>9.699999999999999</v>
@@ -978,7 +978,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>34542271210</v>
+        <v>35499239755</v>
       </c>
       <c r="P6" t="n">
         <v>40350</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>대우건설, 정치적 언급 및 주가 조작 의혹 관련 게시글 다수. 외인 보유율 관련 언급이 있으나 실질적인 주가 흐름에 대한 구체적 팩트 부족.</t>
+          <t>대우건설, 주가조작 의혹 및 정치권 관련 언급으로 부정적 분위기 형성. 외인 보유율 및 뱅크런 관련 우려 제기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주가 조작', '외인 보유율', '뱅크런']</t>
+          <t>['주가조작', '외인보유률', '뱅크런']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,83 +1023,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>216250</v>
+        <v>9070</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.35%</t>
+          <t>'+0.67%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.01</v>
+        <v>1.02</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>127</v>
       </c>
       <c r="F7" t="n">
-        <v>517</v>
+        <v>69</v>
       </c>
       <c r="G7" t="n">
-        <v>1801</v>
+        <v>265</v>
       </c>
       <c r="H7" t="n">
-        <v>45.99</v>
+        <v>1.74</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>215500</v>
+        <v>9010</v>
       </c>
       <c r="K7" t="n">
-        <v>207000</v>
+        <v>8810</v>
       </c>
       <c r="L7" t="n">
-        <v>219500</v>
+        <v>9500</v>
       </c>
       <c r="M7" t="n">
-        <v>206500</v>
+        <v>8510</v>
       </c>
       <c r="N7" t="n">
-        <v>45.98</v>
+        <v>0.72</v>
       </c>
       <c r="O7" t="n">
-        <v>2857621885750</v>
+        <v>150572567670</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>9500</v>
       </c>
       <c r="Q7" t="n">
-        <v>94500</v>
+        <v>2270</v>
       </c>
       <c r="R7" t="n">
-        <v>1564000</v>
+        <v>-235000</v>
       </c>
       <c r="S7" t="n">
-        <v>718000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼성전자, 연기금 이탈 관측 속 외국인 순매수 1위 기록. 주주환원 및 상승 기대감에도 불구하고 실적 부진 우려 상존.</t>
+          <t>HT로보틱스, 시장 전반의 하락세 속에서 특별한 근거 없이 개인 투자자들의 혼란과 손실 경험이 주로 언급됨.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['외국인 순매수', '주주환원', '실적 부진']</t>
+          <t>['로봇주', '개인 투자', '시장']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
@@ -1130,13 +1130,13 @@
         <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F8" t="n">
         <v>37</v>
       </c>
       <c r="G8" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H8" t="n">
         <v>0.06</v>
@@ -1162,7 +1162,7 @@
         <v>0.11</v>
       </c>
       <c r="O8" t="n">
-        <v>29644425495</v>
+        <v>29939783525</v>
       </c>
       <c r="P8" t="n">
         <v>30800</v>
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18220</v>
+        <v>1275000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.98%</t>
+          <t>'+0.24%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="E9" t="n">
-        <v>67</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>42</v>
+        <v>499</v>
       </c>
       <c r="G9" t="n">
-        <v>226</v>
+        <v>1843</v>
       </c>
       <c r="H9" t="n">
-        <v>27.85</v>
+        <v>48.82</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,91 +1239,91 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>18400</v>
+        <v>1272000</v>
       </c>
       <c r="K9" t="n">
-        <v>17690</v>
+        <v>1212000</v>
       </c>
       <c r="L9" t="n">
-        <v>18240</v>
+        <v>1277000</v>
       </c>
       <c r="M9" t="n">
-        <v>17670</v>
+        <v>1208000</v>
       </c>
       <c r="N9" t="n">
-        <v>27.77</v>
+        <v>48.85</v>
       </c>
       <c r="O9" t="n">
-        <v>44764065400</v>
+        <v>3909212072000</v>
       </c>
       <c r="P9" t="n">
-        <v>35350</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>17210</v>
+        <v>465500</v>
       </c>
       <c r="R9" t="n">
-        <v>-633000</v>
+        <v>-34000</v>
       </c>
       <c r="S9" t="n">
-        <v>6000</v>
+        <v>39000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>삼성중공업, 조선주 목표가 하향 조정 및 공매도 지속. 하락세 지속 우려.</t>
+          <t>SK하이닉스, 솔리다임 중복 상장 이슈로 인한 강한 불만 제기. 큰 폭의 손실 언급 및 증시 전반에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['조선주', '공매도', '목표가']</t>
+          <t>['솔리다임', '중복상장', '손실']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1254000</v>
+        <v>18240</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.42%</t>
+          <t>'-0.87%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.03</v>
+        <v>0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>68</v>
       </c>
       <c r="F10" t="n">
-        <v>498</v>
+        <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>1850</v>
+        <v>226</v>
       </c>
       <c r="H10" t="n">
-        <v>48.82</v>
+        <v>27.85</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,60 +1331,60 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1272000</v>
+        <v>18400</v>
       </c>
       <c r="K10" t="n">
-        <v>1212000</v>
+        <v>17690</v>
       </c>
       <c r="L10" t="n">
-        <v>1268000</v>
+        <v>18270</v>
       </c>
       <c r="M10" t="n">
-        <v>1208000</v>
+        <v>17670</v>
       </c>
       <c r="N10" t="n">
-        <v>48.85</v>
+        <v>27.77</v>
       </c>
       <c r="O10" t="n">
-        <v>3707940446500</v>
+        <v>46363551875</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>35350</v>
       </c>
       <c r="Q10" t="n">
-        <v>465500</v>
+        <v>17210</v>
       </c>
       <c r="R10" t="n">
-        <v>-34000</v>
+        <v>-633000</v>
       </c>
       <c r="S10" t="n">
-        <v>39000</v>
+        <v>6000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>SK하이닉스, 솔리다임의 미국 중복상장 관련 금감원 판단에 따른 불확실성 부각. 주가 하락 및 대규모 손실 우려 제기.</t>
+          <t>삼성중공업, 조선주 목표가 하향 조정 및 공매도 지속. 하락세 지속 우려.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['솔리다임', '중복상장', '금감원']</t>
+          <t>['조선주', '공매도', '목표가']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14100</v>
+        <v>14170</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-6.06%</t>
+          <t>'-5.60%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F11" t="n">
         <v>61</v>
       </c>
       <c r="G11" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>43752516585</v>
+        <v>44681336415</v>
       </c>
       <c r="P11" t="n">
         <v>28800</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-7.85%</t>
+          <t>'-7.53%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>31</v>
       </c>
       <c r="G12" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>12368711765</v>
+        <v>12448988884</v>
       </c>
       <c r="P12" t="n">
         <v>1950</v>

--- a/data/trending_integrated_20261019_15.xlsx
+++ b/data/trending_integrated_20261019_15.xlsx
@@ -578,13 +578,13 @@
         <v>0.42</v>
       </c>
       <c r="E2" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="F2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G2" t="n">
-        <v>691</v>
+        <v>701</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>20708828420</v>
+        <v>20735932908</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>스페이스X 로켓 발사대 강관 공급 단독 뉴스 기반으로 급등세. 외인 매수세 유입되며 전고점 돌파 기대.</t>
+          <t>KBI동양철관, 스페이스X 로켓 발사대 강관 공급 계약 체결. 외인 매집 활발.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스페이스X', '강관', '납품']</t>
+          <t>['스페이스X', '강관 공급', '외인 매집']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9700</v>
+        <v>9710</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.79%</t>
+          <t>'+14.91%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F3" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G3" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>40027803035</v>
+        <v>40762031435</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>170700</v>
+        <v>171400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.09%</t>
+          <t>'+2.51%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>63</v>
       </c>
       <c r="G4" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H4" t="n">
         <v>75.02</v>
@@ -794,7 +794,7 @@
         <v>75</v>
       </c>
       <c r="O4" t="n">
-        <v>620476098400</v>
+        <v>636940582550</v>
       </c>
       <c r="P4" t="n">
         <v>243500</v>
@@ -839,83 +839,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>218000</v>
+        <v>9120</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.16%</t>
+          <t>'+1.22%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.01</v>
+        <v>1.02</v>
       </c>
       <c r="E5" t="n">
-        <v>800</v>
+        <v>133</v>
       </c>
       <c r="F5" t="n">
-        <v>506</v>
+        <v>71</v>
       </c>
       <c r="G5" t="n">
-        <v>1811</v>
+        <v>272</v>
       </c>
       <c r="H5" t="n">
-        <v>45.99</v>
+        <v>1.74</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>215500</v>
+        <v>9010</v>
       </c>
       <c r="K5" t="n">
-        <v>207000</v>
+        <v>8810</v>
       </c>
       <c r="L5" t="n">
-        <v>219500</v>
+        <v>9500</v>
       </c>
       <c r="M5" t="n">
-        <v>206500</v>
+        <v>8510</v>
       </c>
       <c r="N5" t="n">
-        <v>45.98</v>
+        <v>0.72</v>
       </c>
       <c r="O5" t="n">
-        <v>2986042845750</v>
+        <v>151913951800</v>
       </c>
       <c r="P5" t="n">
-        <v>374500</v>
+        <v>9500</v>
       </c>
       <c r="Q5" t="n">
-        <v>94500</v>
+        <v>2270</v>
       </c>
       <c r="R5" t="n">
-        <v>1564000</v>
+        <v>-235000</v>
       </c>
       <c r="S5" t="n">
-        <v>718000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>삼성전자, 주주환원 요구와 함께 바닥 다지기 후 상승 기대감 표출. 외인 순매수 기록했으나 종가 하락 및 연기금 이탈 조짐.</t>
+          <t>HT로보틱스, 시장 전반의 하락세 속에서 특별한 근거 없이 개인 투자자들의 혼란과 손실 경험이 주로 언급됨.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['주주환원', '외인순매수', '바닥다지기']</t>
+          <t>['로봇주', '개인 투자', '시장']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14860</v>
+        <v>218000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.88%</t>
+          <t>'+1.16%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>163</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>49</v>
+        <v>508</v>
       </c>
       <c r="G6" t="n">
-        <v>366</v>
+        <v>1814</v>
       </c>
       <c r="H6" t="n">
-        <v>9.699999999999999</v>
+        <v>45.99</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14730</v>
+        <v>215500</v>
       </c>
       <c r="K6" t="n">
-        <v>14500</v>
+        <v>207000</v>
       </c>
       <c r="L6" t="n">
-        <v>15070</v>
+        <v>219500</v>
       </c>
       <c r="M6" t="n">
-        <v>14120</v>
+        <v>206500</v>
       </c>
       <c r="N6" t="n">
-        <v>9.779999999999999</v>
+        <v>45.98</v>
       </c>
       <c r="O6" t="n">
-        <v>35499239755</v>
+        <v>3082087676750</v>
       </c>
       <c r="P6" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>3320</v>
+        <v>94500</v>
       </c>
       <c r="R6" t="n">
-        <v>-83000</v>
+        <v>1564000</v>
       </c>
       <c r="S6" t="n">
-        <v>-106000</v>
+        <v>718000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>대우건설, 주가조작 의혹 및 정치권 관련 언급으로 부정적 분위기 형성. 외인 보유율 및 뱅크런 관련 우려 제기.</t>
+          <t>삼성전자, 주주환원 정책 기대감 속 외국인 순매수 기록. 일부 투자자 부정적 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주가조작', '외인보유률', '뱅크런']</t>
+          <t>['주주환원', '외국인 순매수', '기대감']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9070</v>
+        <v>14890</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.67%</t>
+          <t>'+1.09%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.02</v>
+        <v>-0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>127</v>
+        <v>166</v>
       </c>
       <c r="F7" t="n">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="G7" t="n">
-        <v>265</v>
+        <v>381</v>
       </c>
       <c r="H7" t="n">
-        <v>1.74</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9010</v>
+        <v>14730</v>
       </c>
       <c r="K7" t="n">
-        <v>8810</v>
+        <v>14500</v>
       </c>
       <c r="L7" t="n">
-        <v>9500</v>
+        <v>15070</v>
       </c>
       <c r="M7" t="n">
-        <v>8510</v>
+        <v>14120</v>
       </c>
       <c r="N7" t="n">
-        <v>0.72</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>150572567670</v>
+        <v>36103153450</v>
       </c>
       <c r="P7" t="n">
-        <v>9500</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>2270</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>-235000</v>
+        <v>-83000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-106000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>HT로보틱스, 시장 전반의 하락세 속에서 특별한 근거 없이 개인 투자자들의 혼란과 손실 경험이 주로 언급됨.</t>
+          <t>대우건설, 주가조작 의혹 및 정치권 관련 언급으로 부정적 분위기 형성. 외인 보유율 및 뱅크런 관련 우려 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['로봇주', '개인 투자', '시장']</t>
+          <t>['주가조작', '외인보유률', '뱅크런']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15000</v>
+        <v>15020</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.33%</t>
+          <t>'+0.47%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1162,7 +1162,7 @@
         <v>0.11</v>
       </c>
       <c r="O8" t="n">
-        <v>29939783525</v>
+        <v>30242625975</v>
       </c>
       <c r="P8" t="n">
         <v>30800</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1275000</v>
+        <v>1274000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.24%</t>
+          <t>'+0.16%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="G9" t="n">
-        <v>1843</v>
+        <v>1865</v>
       </c>
       <c r="H9" t="n">
         <v>48.82</v>
@@ -1254,7 +1254,7 @@
         <v>48.85</v>
       </c>
       <c r="O9" t="n">
-        <v>3909212072000</v>
+        <v>4032574152000</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>SK하이닉스, 솔리다임 중복 상장 이슈로 인한 강한 불만 제기. 큰 폭의 손실 언급 및 증시 전반에 대한 부정적 전망.</t>
+          <t>SK하이닉스, 솔리다임 중복상장 이슈로 인한 투자자 불만 제기. 실적 발표 예정.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['솔리다임', '중복상장', '손실']</t>
+          <t>['솔리다임', '중복상장', '실적발표']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18240</v>
+        <v>18260</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.87%</t>
+          <t>'-0.76%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="H10" t="n">
         <v>27.85</v>
@@ -1346,7 +1346,7 @@
         <v>27.77</v>
       </c>
       <c r="O10" t="n">
-        <v>46363551875</v>
+        <v>47443473755</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1395,21 +1395,21 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14170</v>
+        <v>14380</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-5.60%</t>
+          <t>'-4.20%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F11" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G11" t="n">
         <v>109</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>44681336415</v>
+        <v>45853405005</v>
       </c>
       <c r="P11" t="n">
         <v>28800</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1166</v>
+        <v>1160</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-7.53%</t>
+          <t>'-8.01%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G12" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>12448988884</v>
+        <v>12589786535</v>
       </c>
       <c r="P12" t="n">
         <v>1950</v>

--- a/data/trending_integrated_20261019_15.xlsx
+++ b/data/trending_integrated_20261019_15.xlsx
@@ -578,13 +578,13 @@
         <v>0.42</v>
       </c>
       <c r="E2" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F2" t="n">
         <v>82</v>
       </c>
       <c r="G2" t="n">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>20735932908</v>
+        <v>20736299988</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9710</v>
+        <v>9720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.91%</t>
+          <t>'+15.03%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>81</v>
       </c>
       <c r="G3" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>40762031435</v>
+        <v>41335025435</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>171400</v>
+        <v>170900</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.51%</t>
+          <t>'+2.21%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F4" t="n">
         <v>63</v>
       </c>
       <c r="G4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H4" t="n">
         <v>75.02</v>
@@ -794,7 +794,7 @@
         <v>75</v>
       </c>
       <c r="O4" t="n">
-        <v>636940582550</v>
+        <v>655240212750</v>
       </c>
       <c r="P4" t="n">
         <v>243500</v>
@@ -839,70 +839,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9120</v>
+        <v>14950</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.22%</t>
+          <t>'+1.49%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.02</v>
+        <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="F5" t="n">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="G5" t="n">
-        <v>272</v>
+        <v>386</v>
       </c>
       <c r="H5" t="n">
-        <v>1.74</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9010</v>
+        <v>14730</v>
       </c>
       <c r="K5" t="n">
-        <v>8810</v>
+        <v>14500</v>
       </c>
       <c r="L5" t="n">
-        <v>9500</v>
+        <v>15070</v>
       </c>
       <c r="M5" t="n">
-        <v>8510</v>
+        <v>14120</v>
       </c>
       <c r="N5" t="n">
-        <v>0.72</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>151913951800</v>
+        <v>37042596500</v>
       </c>
       <c r="P5" t="n">
-        <v>9500</v>
+        <v>40350</v>
       </c>
       <c r="Q5" t="n">
-        <v>2270</v>
+        <v>3320</v>
       </c>
       <c r="R5" t="n">
-        <v>-235000</v>
+        <v>-83000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-106000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>HT로보틱스, 시장 전반의 하락세 속에서 특별한 근거 없이 개인 투자자들의 혼란과 손실 경험이 주로 언급됨.</t>
+          <t>대우건설, 주가 조작 및 이재명 대통령 관련 언급이 주를 이루며, 외인보유율 관련 내용 언급. 객관적 근거 부족.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['로봇주', '개인 투자', '시장']</t>
+          <t>['주가조작', '외인보유율', '이재명']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>218000</v>
+        <v>9120</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.16%</t>
+          <t>'+1.22%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.01</v>
+        <v>1.02</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>136</v>
       </c>
       <c r="F6" t="n">
-        <v>508</v>
+        <v>71</v>
       </c>
       <c r="G6" t="n">
-        <v>1814</v>
+        <v>277</v>
       </c>
       <c r="H6" t="n">
-        <v>45.99</v>
+        <v>1.74</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>215500</v>
+        <v>9010</v>
       </c>
       <c r="K6" t="n">
-        <v>207000</v>
+        <v>8810</v>
       </c>
       <c r="L6" t="n">
-        <v>219500</v>
+        <v>9500</v>
       </c>
       <c r="M6" t="n">
-        <v>206500</v>
+        <v>8510</v>
       </c>
       <c r="N6" t="n">
-        <v>45.98</v>
+        <v>0.72</v>
       </c>
       <c r="O6" t="n">
-        <v>3082087676750</v>
+        <v>152552953720</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>9500</v>
       </c>
       <c r="Q6" t="n">
-        <v>94500</v>
+        <v>2270</v>
       </c>
       <c r="R6" t="n">
-        <v>1564000</v>
+        <v>-235000</v>
       </c>
       <c r="S6" t="n">
-        <v>718000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성전자, 주주환원 정책 기대감 속 외국인 순매수 기록. 일부 투자자 부정적 전망.</t>
+          <t>HT로보틱스, 시장 전반의 반등 속에서 홀로 하락하는 모습에 대한 실망감 표출. 분석글 언급 후 급락하는 패턴에 대한 지적.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주주환원', '외국인 순매수', '기대감']</t>
+          <t>['로봇주', '급반등', '분석글']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14890</v>
+        <v>218000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.09%</t>
+          <t>'+1.16%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>166</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>49</v>
+        <v>517</v>
       </c>
       <c r="G7" t="n">
-        <v>381</v>
+        <v>1827</v>
       </c>
       <c r="H7" t="n">
-        <v>9.699999999999999</v>
+        <v>45.99</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14730</v>
+        <v>215500</v>
       </c>
       <c r="K7" t="n">
-        <v>14500</v>
+        <v>207000</v>
       </c>
       <c r="L7" t="n">
-        <v>15070</v>
+        <v>219500</v>
       </c>
       <c r="M7" t="n">
-        <v>14120</v>
+        <v>206500</v>
       </c>
       <c r="N7" t="n">
-        <v>9.779999999999999</v>
+        <v>45.98</v>
       </c>
       <c r="O7" t="n">
-        <v>36103153450</v>
+        <v>3374908110750</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>-83000</v>
+        <v>1564000</v>
       </c>
       <c r="S7" t="n">
-        <v>-106000</v>
+        <v>718000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>대우건설, 주가조작 의혹 및 정치권 관련 언급으로 부정적 분위기 형성. 외인 보유율 및 뱅크런 관련 우려 제기.</t>
+          <t>삼성전자, 주주환원 요구와 함께 바닥 다지기 후 상승 기대감 표출. 그러나 외국인 매수세 유입에도 불구하고 종가 하락 및 연기금 이탈 조짐 관찰.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주가조작', '외인보유률', '뱅크런']</t>
+          <t>['주주환원', '바닥다지기', '외국인매수']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1130,10 +1130,10 @@
         <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G8" t="n">
         <v>91</v>
@@ -1162,7 +1162,7 @@
         <v>0.11</v>
       </c>
       <c r="O8" t="n">
-        <v>30242625975</v>
+        <v>30391669435</v>
       </c>
       <c r="P8" t="n">
         <v>30800</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1274000</v>
+        <v>1277000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.16%</t>
+          <t>'+0.39%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="G9" t="n">
-        <v>1865</v>
+        <v>1829</v>
       </c>
       <c r="H9" t="n">
         <v>48.82</v>
@@ -1254,7 +1254,7 @@
         <v>48.85</v>
       </c>
       <c r="O9" t="n">
-        <v>4032574152000</v>
+        <v>4336844942000</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>SK하이닉스, 솔리다임 중복상장 이슈로 인한 투자자 불만 제기. 실적 발표 예정.</t>
+          <t>SK하이닉스, 상당한 손실 발생과 함께 솔리다임 중복 상장 이슈로 인한 부정적 전망. 실적 발표를 앞두고 불확실성 증대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18260</v>
+        <v>18300</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.76%</t>
+          <t>'-0.54%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H10" t="n">
         <v>27.85</v>
@@ -1337,7 +1337,7 @@
         <v>17690</v>
       </c>
       <c r="L10" t="n">
-        <v>18270</v>
+        <v>18300</v>
       </c>
       <c r="M10" t="n">
         <v>17670</v>
@@ -1346,7 +1346,7 @@
         <v>27.77</v>
       </c>
       <c r="O10" t="n">
-        <v>47443473755</v>
+        <v>51185000255</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14380</v>
+        <v>14500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.20%</t>
+          <t>'-3.40%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F11" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G11" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>45853405005</v>
+        <v>46512647505</v>
       </c>
       <c r="P11" t="n">
         <v>28800</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-8.01%</t>
+          <t>'-7.69%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F12" t="n">
         <v>32</v>
       </c>
       <c r="G12" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>12589786535</v>
+        <v>12640851215</v>
       </c>
       <c r="P12" t="n">
         <v>1950</v>

--- a/data/trending_integrated_20261019_15.xlsx
+++ b/data/trending_integrated_20261019_15.xlsx
@@ -571,20 +571,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+29.96%</t>
+          <t>'+38.84%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.42</v>
       </c>
       <c r="E2" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F2" t="n">
         <v>82</v>
       </c>
       <c r="G2" t="n">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1345</v>
+        <v>1259</v>
       </c>
       <c r="K2" t="n">
-        <v>1432</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1748</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1386</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>20736299988</v>
+        <v>20736000000</v>
       </c>
       <c r="P2" t="n">
-        <v>2970</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>890</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>918000</v>
@@ -676,7 +676,7 @@
         <v>81</v>
       </c>
       <c r="G3" t="n">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>41335025435</v>
+        <v>41338038635</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -762,13 +762,13 @@
         <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F4" t="n">
         <v>63</v>
       </c>
       <c r="G4" t="n">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="H4" t="n">
         <v>75.02</v>
@@ -794,7 +794,7 @@
         <v>75</v>
       </c>
       <c r="O4" t="n">
-        <v>655240212750</v>
+        <v>655321732050</v>
       </c>
       <c r="P4" t="n">
         <v>243500</v>
@@ -854,13 +854,13 @@
         <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F5" t="n">
         <v>49</v>
       </c>
       <c r="G5" t="n">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="H5" t="n">
         <v>9.699999999999999</v>
@@ -886,7 +886,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>37042596500</v>
+        <v>37062883650</v>
       </c>
       <c r="P5" t="n">
         <v>40350</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>대우건설, 주가 조작 및 이재명 대통령 관련 언급이 주를 이루며, 외인보유율 관련 내용 언급. 객관적 근거 부족.</t>
+          <t>대우건설, 주가 상승에 대한 기대감과 함께 주가 조작 및 외인 보유율 관련 의혹 제기. 대차 해지 중요성 강조.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['주가조작', '외인보유율', '이재명']</t>
+          <t>['주가조작', '외인보유율', '대차해지']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -949,10 +949,10 @@
         <v>136</v>
       </c>
       <c r="F6" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G6" t="n">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="H6" t="n">
         <v>1.74</v>
@@ -978,7 +978,7 @@
         <v>0.72</v>
       </c>
       <c r="O6" t="n">
-        <v>152552953720</v>
+        <v>152566433080</v>
       </c>
       <c r="P6" t="n">
         <v>9500</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>HT로보틱스, 시장 전반의 반등 속에서 홀로 하락하는 모습에 대한 실망감 표출. 분석글 언급 후 급락하는 패턴에 대한 지적.</t>
+          <t>HT로보틱스, 단기 과열 구간 진입 및 해제 관련 언급. 시장 전반의 급반등과 달리 혼자 움직이지 않는다는 점 지적.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['로봇주', '급반등', '분석글']</t>
+          <t>['단기과열', '주포', '로봇주']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="G7" t="n">
-        <v>1827</v>
+        <v>1874</v>
       </c>
       <c r="H7" t="n">
         <v>45.99</v>
@@ -1070,7 +1070,7 @@
         <v>45.98</v>
       </c>
       <c r="O7" t="n">
-        <v>3374908110750</v>
+        <v>3375305088750</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼성전자, 주주환원 요구와 함께 바닥 다지기 후 상승 기대감 표출. 그러나 외국인 매수세 유입에도 불구하고 종가 하락 및 연기금 이탈 조짐 관찰.</t>
+          <t>삼성전자의 바닥 다지기 완료 및 상승 전환 기대감. 다만, 주주환원 및 일부 투자자 손실 발생 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주주환원', '바닥다지기', '외국인매수']</t>
+          <t>['주주환원', '바닥다지기', '상승전망']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1130,13 +1130,13 @@
         <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G8" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H8" t="n">
         <v>0.06</v>
@@ -1162,7 +1162,7 @@
         <v>0.11</v>
       </c>
       <c r="O8" t="n">
-        <v>30391669435</v>
+        <v>30417113315</v>
       </c>
       <c r="P8" t="n">
         <v>30800</v>
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="G9" t="n">
-        <v>1829</v>
+        <v>1880</v>
       </c>
       <c r="H9" t="n">
         <v>48.82</v>
@@ -1254,7 +1254,7 @@
         <v>48.85</v>
       </c>
       <c r="O9" t="n">
-        <v>4336844942000</v>
+        <v>4338736179000</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>SK하이닉스, 상당한 손실 발생과 함께 솔리다임 중복 상장 이슈로 인한 부정적 전망. 실적 발표를 앞두고 불확실성 증대.</t>
+          <t>SK하이닉스, 솔리다임 관련 악재 및 주가 하락에 대한 불만. 실적 발표 및 반등 기대감 혼재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['솔리다임', '중복상장', '실적발표']</t>
+          <t>['솔리다임', '실적발표', '주가하락']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1314,13 +1314,13 @@
         <v>0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F10" t="n">
         <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H10" t="n">
         <v>27.85</v>
@@ -1346,7 +1346,7 @@
         <v>27.77</v>
       </c>
       <c r="O10" t="n">
-        <v>51185000255</v>
+        <v>51186610655</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1406,13 +1406,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F11" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G11" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>46512647505</v>
+        <v>46555437005</v>
       </c>
       <c r="P11" t="n">
         <v>28800</v>
@@ -1498,13 +1498,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G12" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>12640851215</v>
+        <v>12641422739</v>
       </c>
       <c r="P12" t="n">
         <v>1950</v>
